--- a/artfynd/A 32318-2026 artfynd.xlsx
+++ b/artfynd/A 32318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137382744</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381526</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381588</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137382092</v>
       </c>
       <c r="B5" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137382746</v>
       </c>
       <c r="B6" t="n">
-        <v>96890</v>
+        <v>96896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381564</v>
       </c>
       <c r="B7" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137382049</v>
       </c>
       <c r="B8" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32318-2026 artfynd.xlsx
+++ b/artfynd/A 32318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137382744</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381526</v>
       </c>
       <c r="B3" t="n">
-        <v>93488</v>
+        <v>93500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381588</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137382092</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137382746</v>
       </c>
       <c r="B6" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381564</v>
       </c>
       <c r="B7" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137382049</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32318-2026 artfynd.xlsx
+++ b/artfynd/A 32318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137382744</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381526</v>
       </c>
       <c r="B3" t="n">
-        <v>93500</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381588</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137382092</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137382746</v>
       </c>
       <c r="B6" t="n">
-        <v>96908</v>
+        <v>96909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381564</v>
       </c>
       <c r="B7" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137382049</v>
       </c>
       <c r="B8" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32318-2026 artfynd.xlsx
+++ b/artfynd/A 32318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137382744</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381526</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381588</v>
       </c>
       <c r="B4" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137382092</v>
       </c>
       <c r="B5" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137382746</v>
       </c>
       <c r="B6" t="n">
-        <v>96909</v>
+        <v>96912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381564</v>
       </c>
       <c r="B7" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137382049</v>
       </c>
       <c r="B8" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32318-2026 artfynd.xlsx
+++ b/artfynd/A 32318-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137382744</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,27 +792,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137381526</v>
+        <v>137381588</v>
       </c>
       <c r="B3" t="n">
-        <v>93504</v>
+        <v>93505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1440</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381526</t>
+          <t>https://artportalen.se/Sighting/137381588</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137381588</v>
+        <v>137382092</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järnholmen, Sm</t>
+          <t>Fridhem, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548793</v>
+        <v>548709</v>
       </c>
       <c r="R4" t="n">
-        <v>6383181</v>
+        <v>6383184</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,38 +1010,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381588</t>
+          <t>https://artportalen.se/Sighting/137382092</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137382092</v>
+        <v>137382746</v>
       </c>
       <c r="B5" t="n">
-        <v>93501</v>
+        <v>96916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,51 +1122,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382092</t>
+          <t>https://artportalen.se/Sighting/137382746</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137382746</v>
+        <v>137381564</v>
       </c>
       <c r="B6" t="n">
-        <v>96912</v>
+        <v>93527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fridhem, Sm</t>
+          <t>Järnholmen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548709</v>
+        <v>548793</v>
       </c>
       <c r="R6" t="n">
-        <v>6383184</v>
+        <v>6383181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382746</t>
+          <t>https://artportalen.se/Sighting/137381564</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137381564</v>
+        <v>137382049</v>
       </c>
       <c r="B7" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,14 +1271,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Järnholmen, Sm</t>
+          <t>Fridhem, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548793</v>
+        <v>548709</v>
       </c>
       <c r="R7" t="n">
-        <v>6383181</v>
+        <v>6383184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,118 +1345,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137381564</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>137382049</v>
-      </c>
-      <c r="B8" t="n">
-        <v>93523</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Fridhem, Sm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>548709</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6383184</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137382049</t>
         </is>
@@ -1470,7 +1358,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
